--- a/templates/ecosystem/Master_Writing_Ecosystem.xlsx
+++ b/templates/ecosystem/Master_Writing_Ecosystem.xlsx
@@ -16056,7 +16056,7 @@
     </row>
     <row r="5" ht="19.5" customHeight="1">
       <c r="A5" s="102" t="n">
-        <v>46388</v>
+        <v>46306</v>
       </c>
       <c r="B5" s="103" t="str">
         <v>The Silver Chronicles</v>
